--- a/artfynd/A 20501-2021 artfynd.xlsx
+++ b/artfynd/A 20501-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923546</v>
       </c>
       <c r="B2" t="n">
-        <v>57501</v>
+        <v>57502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20501-2021 artfynd.xlsx
+++ b/artfynd/A 20501-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923546</v>
       </c>
       <c r="B2" t="n">
-        <v>57502</v>
+        <v>57506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20501-2021 artfynd.xlsx
+++ b/artfynd/A 20501-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923546</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20501-2021 artfynd.xlsx
+++ b/artfynd/A 20501-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923546</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>57675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20501-2021 artfynd.xlsx
+++ b/artfynd/A 20501-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923546</v>
       </c>
       <c r="B2" t="n">
-        <v>57675</v>
+        <v>57701</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20501-2021 artfynd.xlsx
+++ b/artfynd/A 20501-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923546</v>
       </c>
       <c r="B2" t="n">
-        <v>57701</v>
+        <v>57703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20501-2021 artfynd.xlsx
+++ b/artfynd/A 20501-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923546</v>
       </c>
       <c r="B2" t="n">
-        <v>57703</v>
+        <v>57711</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
